--- a/event_registration_forms/016_ai_event_registration_form--event_registration_forms.xlsx
+++ b/event_registration_forms/016_ai_event_registration_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -965,8 +965,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -994,12 +994,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'standard_attendee',_'value':_'standard'}</t>
+          <t>standard_attendee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Standard Attendee', 'value': 'standard'}</t>
+          <t>Standard Attendee</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'student_/_academic',_'value':_'student'}</t>
+          <t>student_/_academic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Student / Academic', 'value': 'student'}</t>
+          <t>Student / Academic</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'speaker_/_vip',_'value':_'speaker'}</t>
+          <t>speaker_/_vip</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Speaker / VIP', 'value': 'speaker'}</t>
+          <t>Speaker / VIP</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'press_/_media',_'value':_'press'}</t>
+          <t>press_/_media</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Press / Media', 'value': 'press'}</t>
+          <t>Press / Media</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'exhibitor',_'value':_'exhibitor'}</t>
+          <t>exhibitor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Exhibitor', 'value': 'exhibitor'}</t>
+          <t>Exhibitor</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'expert_(researcher/developer)',_'value':_'expert'}</t>
+          <t>expert_(researcher/developer)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Expert (Researcher/Developer)', 'value': 'expert'}</t>
+          <t>Expert (Researcher/Developer)</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'intermediate_(power_user/business_leader)',_'value':_'intermediate'}</t>
+          <t>intermediate_(power_user/business_leader)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Intermediate (Power User/Business Leader)', 'value': 'intermediate'}</t>
+          <t>Intermediate (Power User/Business Leader)</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'novice_(curious/beginner)',_'value':_'novice'}</t>
+          <t>novice_(curious/beginner)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Novice (Curious/Beginner)', 'value': 'novice'}</t>
+          <t>Novice (Curious/Beginner)</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'generative_ai_&amp;_llms',_'value':_'gen_ai'}</t>
+          <t>generative_ai_&amp;_llms</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Generative AI &amp; LLMs', 'value': 'gen_ai'}</t>
+          <t>Generative AI &amp; LLMs</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'ai_strategy_&amp;_governance',_'value':_'strategy'}</t>
+          <t>ai_strategy_&amp;_governance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'AI Strategy &amp; Governance', 'value': 'strategy'}</t>
+          <t>AI Strategy &amp; Governance</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'machine_learning_operations_(mlops)',_'value':_'mlops'}</t>
+          <t>machine_learning_operations_(mlops)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Machine Learning Operations (MLOps)', 'value': 'mlops'}</t>
+          <t>Machine Learning Operations (MLOps)</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'ethical_ai_&amp;_regulation',_'value':_'ethics'}</t>
+          <t>ethical_ai_&amp;_regulation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Ethical AI &amp; Regulation', 'value': 'ethics'}</t>
+          <t>Ethical AI &amp; Regulation</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'ai_in_business_&amp;_finance',_'value':_'business'}</t>
+          <t>ai_in_business_&amp;_finance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'AI in Business &amp; Finance', 'value': 'business'}</t>
+          <t>AI in Business &amp; Finance</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'no_restrictions',_'value':_'none'}</t>
+          <t>no_restrictions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'No restrictions', 'value': 'none'}</t>
+          <t>No restrictions</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'vegetarian',_'value':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Vegetarian', 'value': 'vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'vegan',_'value':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Vegan', 'value': 'vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'gluten-free',_'value':_'gluten_free'}</t>
+          <t>gluten-free</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Gluten-Free', 'value': 'gluten_free'}</t>
+          <t>Gluten-Free</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'halal',_'value':_'halal'}</t>
+          <t>halal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Halal', 'value': 'halal'}</t>
+          <t>Halal</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'kosher',_'value':_'kosher'}</t>
+          <t>kosher</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Kosher', 'value': 'kosher'}</t>
+          <t>Kosher</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'nut_allergy',_'value':_'nut_allergy'}</t>
+          <t>nut_allergy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Nut Allergy', 'value': 'nut_allergy'}</t>
+          <t>Nut Allergy</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_want_to_network',_'value':_true}</t>
+          <t>yes,_i_want_to_network</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I want to network', 'value': True}</t>
+          <t>Yes, I want to network</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'no,_keep_my_info_private',_'value':_false}</t>
+          <t>no,_keep_my_info_private</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'No, keep my info private', 'value': False}</t>
+          <t>No, keep my info private</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'small',_'value':_'s'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Small', 'value': 's'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_'m'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 'm'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'large',_'value':_'l'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Large', 'value': 'l'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'xl',_'value':_'xl'}</t>
+          <t>xl</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'XL', 'value': 'xl'}</t>
+          <t>XL</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'xxl',_'value':_'xxl'}</t>
+          <t>xxl</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'XXL', 'value': 'xxl'}</t>
+          <t>XXL</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'email_newsletter',_'value':_'newsletter'}</t>
+          <t>email_newsletter</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Email Newsletter', 'value': 'newsletter'}</t>
+          <t>Email Newsletter</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'linkedin',_'value':_'linkedin'}</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'LinkedIn', 'value': 'linkedin'}</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'colleague_referral',_'value':_'referral'}</t>
+          <t>colleague_referral</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Colleague Referral', 'value': 'referral'}</t>
+          <t>Colleague Referral</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'professional_association',_'value':_'association'}</t>
+          <t>professional_association</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Professional Association', 'value': 'association'}</t>
+          <t>Professional Association</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_agree',_'value':_true}</t>
+          <t>yes,_i_agree</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I agree', 'value': True}</t>
+          <t>Yes, I agree</t>
         </is>
       </c>
     </row>
